--- a/file/table/BogotaRiverLevels.xlsx
+++ b/file/table/BogotaRiverLevels.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30301"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30304"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.WREM\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90C0BD65-0809-4DA4-82C4-FDFE93C0EB04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B437BD-7D26-47BB-AE04-F9FF84897BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" xr2:uid="{2255F479-0D41-4B39-BE5A-1B1436E09AAA}"/>
   </bookViews>
   <sheets>
     <sheet name="PTE LA VIRGEN   21208110 " sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
+    <sheet name="HEC-RAS" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="45">
   <si>
     <t>Date</t>
   </si>
@@ -109,6 +110,69 @@
   </si>
   <si>
     <t>z2, Talud derecho (z:1)</t>
+  </si>
+  <si>
+    <t>L, longitud canal (m)</t>
+  </si>
+  <si>
+    <t>Estación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTE LA VIRGEN   21208110 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Time (hr)</t>
+  </si>
+  <si>
+    <t>Step</t>
+  </si>
+  <si>
+    <t>River</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reach</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> RS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Station</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Elevation</t>
+  </si>
+  <si>
+    <t>River1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reach1</t>
+  </si>
+  <si>
+    <t>HEC-RAS 1D/2D</t>
+  </si>
+  <si>
+    <t>1D cross-section values</t>
+  </si>
+  <si>
+    <t>Schematic X</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Schematic Y</t>
+  </si>
+  <si>
+    <t>1D river coordinates</t>
+  </si>
+  <si>
+    <t>Distributed flow with a triangular unitary hydrograph (UH)</t>
+  </si>
+  <si>
+    <t>Time to peak: 1.5 hr</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Flow (m³/s, cms)</t>
+  </si>
+  <si>
+    <t>s, pendiente crítica (m/m)</t>
   </si>
 </sst>
 </file>
@@ -258,7 +322,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -302,6 +366,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -355,7 +428,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$C$20</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$C$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -378,7 +451,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$B$21:$B$81</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$B$24:$B$84</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="61"/>
@@ -570,7 +643,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$C$21:$C$81</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$C$24:$C$84</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="61"/>
@@ -772,7 +845,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$D$20</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$D$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -798,7 +871,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$B$21:$B$81</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$B$24:$B$84</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="61"/>
@@ -990,7 +1063,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$D$21:$D$81</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$D$24:$D$84</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="61"/>
@@ -1192,7 +1265,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$E$20</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$E$23</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1215,7 +1288,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$B$21:$B$81</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$B$24:$B$84</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="61"/>
@@ -1407,7 +1480,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'PTE LA VIRGEN   21208110 '!$E$21:$E$81</c:f>
+              <c:f>'PTE LA VIRGEN   21208110 '!$E$24:$E$84</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="61"/>
@@ -2388,7 +2461,7 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>402168</xdr:colOff>
-      <xdr:row>17</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>16934</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -2734,17 +2807,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F844144-91FE-4A53-945E-2FBA9C929155}">
-  <dimension ref="B2:E81"/>
+  <dimension ref="B2:E84"/>
   <sheetFormatPr defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.64453125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="20.29296875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="22.703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="13.87890625" style="2" customWidth="1"/>
     <col min="4" max="5" width="11.234375" style="2" customWidth="1"/>
     <col min="6" max="16384" width="8.9375" style="3"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.5">
       <c r="B2" s="14" t="s">
         <v>9</v>
       </c>
@@ -2752,226 +2825,202 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:3" ht="32.700000000000003" x14ac:dyDescent="0.5">
       <c r="B3" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B4" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C4" s="11">
         <v>140</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B4" s="10" t="s">
+    <row r="5" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="11">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C6" s="11">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B5" s="10" t="s">
+    <row r="7" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B7" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C7" s="11">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B6" s="10" t="s">
+    <row r="8" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B8" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="11">
+      <c r="C8" s="11">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B7" s="10" t="s">
+    <row r="9" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B9" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C9" s="11">
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B8" s="10" t="s">
+    <row r="10" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B10" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C10" s="11">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B9" s="10" t="s">
+    <row r="11" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B11" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C11" s="11">
         <v>0.05</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B10" s="10" t="s">
+    <row r="12" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B12" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C12" s="11">
         <v>0.06</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B11" s="10" t="s">
+    <row r="13" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B13" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C13" s="11">
         <v>6.9999999999999994E-5</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B12" s="10" t="s">
+    <row r="14" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B14" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="11">
+        <v>1.1424E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B15" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C15" s="11">
         <v>4879508</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B13" s="10" t="s">
+    <row r="16" spans="2:3" x14ac:dyDescent="0.5">
+      <c r="B16" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C16" s="11">
         <v>2088675</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B14" s="10" t="s">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B17" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C17" s="11">
         <v>2539.84</v>
       </c>
     </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B15" s="8" t="s">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B18" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="11">
-        <v>2545.71</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B16" s="8" t="s">
+      <c r="C18" s="11">
+        <v>2545.71</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B19" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C16" s="11">
-        <v>2546.77</v>
-      </c>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B17" s="8" t="s">
+      <c r="C19" s="11">
+        <v>2546.77</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="5"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B20" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="9">
-        <f>C15-$C$14</f>
+      <c r="C20" s="9">
+        <f>C18-$C$17</f>
         <v>5.8699999999998909</v>
       </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B18" s="12" t="s">
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B21" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="13">
-        <f>C16-$C$14</f>
+      <c r="C21" s="13">
+        <f>C19-$C$17</f>
         <v>6.9299999999998363</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B20" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="3"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B23" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D23" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B21" s="6">
-        <v>46149</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2541.5</v>
-      </c>
-      <c r="D21" s="2">
-        <f t="shared" ref="D21:D52" si="0">$C$15</f>
-        <v>2545.71</v>
-      </c>
-      <c r="E21" s="2">
-        <f t="shared" ref="E21:E52" si="1">$C$16</f>
-        <v>2546.77</v>
-      </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B22" s="6">
-        <v>46150</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2541.4</v>
-      </c>
-      <c r="D22" s="2">
-        <f t="shared" si="0"/>
-        <v>2545.71</v>
-      </c>
-      <c r="E22" s="2">
-        <f t="shared" si="1"/>
-        <v>2546.77</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.5">
-      <c r="B23" s="6">
-        <v>46151</v>
-      </c>
-      <c r="C23" s="7">
-        <v>2541.1999999999998</v>
-      </c>
-      <c r="D23" s="2">
-        <f t="shared" si="0"/>
-        <v>2545.71</v>
-      </c>
-      <c r="E23" s="2">
-        <f t="shared" si="1"/>
-        <v>2546.77</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B24" s="6">
-        <v>46152</v>
+        <v>46149</v>
       </c>
       <c r="C24" s="7">
-        <v>2541.1</v>
+        <v>2541.5</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D24:D55" si="0">$C$18</f>
         <v>2545.71</v>
       </c>
       <c r="E24" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E24:E55" si="1">$C$19</f>
         <v>2546.77</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B25" s="6">
-        <v>46153</v>
+        <v>46150</v>
       </c>
       <c r="C25" s="7">
-        <v>2541.1999999999998</v>
+        <v>2541.4</v>
       </c>
       <c r="D25" s="2">
         <f t="shared" si="0"/>
@@ -2984,10 +3033,10 @@
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B26" s="6">
-        <v>46154</v>
+        <v>46151</v>
       </c>
       <c r="C26" s="7">
-        <v>2541.1</v>
+        <v>2541.1999999999998</v>
       </c>
       <c r="D26" s="2">
         <f t="shared" si="0"/>
@@ -3000,10 +3049,10 @@
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B27" s="6">
-        <v>46155</v>
+        <v>46152</v>
       </c>
       <c r="C27" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.1</v>
       </c>
       <c r="D27" s="2">
         <f t="shared" si="0"/>
@@ -3016,10 +3065,10 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B28" s="6">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="C28" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.1999999999998</v>
       </c>
       <c r="D28" s="2">
         <f t="shared" si="0"/>
@@ -3032,10 +3081,10 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B29" s="6">
-        <v>46157</v>
+        <v>46154</v>
       </c>
       <c r="C29" s="7">
-        <v>2541.4</v>
+        <v>2541.1</v>
       </c>
       <c r="D29" s="2">
         <f t="shared" si="0"/>
@@ -3048,10 +3097,10 @@
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B30" s="6">
-        <v>46158</v>
+        <v>46155</v>
       </c>
       <c r="C30" s="7">
-        <v>2541.4</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D30" s="2">
         <f t="shared" si="0"/>
@@ -3064,7 +3113,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B31" s="6">
-        <v>46159</v>
+        <v>46156</v>
       </c>
       <c r="C31" s="7">
         <v>2541.3000000000002</v>
@@ -3080,10 +3129,10 @@
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B32" s="6">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="C32" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.4</v>
       </c>
       <c r="D32" s="2">
         <f t="shared" si="0"/>
@@ -3096,10 +3145,10 @@
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B33" s="6">
-        <v>46161</v>
+        <v>46158</v>
       </c>
       <c r="C33" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.4</v>
       </c>
       <c r="D33" s="2">
         <f t="shared" si="0"/>
@@ -3112,7 +3161,7 @@
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B34" s="6">
-        <v>46162</v>
+        <v>46159</v>
       </c>
       <c r="C34" s="7">
         <v>2541.3000000000002</v>
@@ -3128,10 +3177,10 @@
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B35" s="6">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="C35" s="7">
-        <v>2541.1999999999998</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D35" s="2">
         <f t="shared" si="0"/>
@@ -3144,7 +3193,7 @@
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B36" s="6">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="C36" s="7">
         <v>2541.3000000000002</v>
@@ -3160,7 +3209,7 @@
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B37" s="6">
-        <v>46165</v>
+        <v>46162</v>
       </c>
       <c r="C37" s="7">
         <v>2541.3000000000002</v>
@@ -3176,10 +3225,10 @@
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B38" s="6">
-        <v>46166</v>
+        <v>46163</v>
       </c>
       <c r="C38" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.1999999999998</v>
       </c>
       <c r="D38" s="2">
         <f t="shared" si="0"/>
@@ -3192,10 +3241,10 @@
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B39" s="6">
-        <v>46167</v>
+        <v>46164</v>
       </c>
       <c r="C39" s="7">
-        <v>2541.4</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D39" s="2">
         <f t="shared" si="0"/>
@@ -3208,10 +3257,10 @@
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B40" s="6">
-        <v>46168</v>
+        <v>46165</v>
       </c>
       <c r="C40" s="7">
-        <v>2541.4</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D40" s="2">
         <f t="shared" si="0"/>
@@ -3224,10 +3273,10 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B41" s="6">
-        <v>46169</v>
+        <v>46166</v>
       </c>
       <c r="C41" s="7">
-        <v>2541.5</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D41" s="2">
         <f t="shared" si="0"/>
@@ -3240,10 +3289,10 @@
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B42" s="6">
-        <v>46170</v>
+        <v>46167</v>
       </c>
       <c r="C42" s="7">
-        <v>2541.6</v>
+        <v>2541.4</v>
       </c>
       <c r="D42" s="2">
         <f t="shared" si="0"/>
@@ -3256,10 +3305,10 @@
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B43" s="6">
-        <v>46171</v>
+        <v>46168</v>
       </c>
       <c r="C43" s="7">
-        <v>2541.8000000000002</v>
+        <v>2541.4</v>
       </c>
       <c r="D43" s="2">
         <f t="shared" si="0"/>
@@ -3272,10 +3321,10 @@
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B44" s="6">
-        <v>46172</v>
+        <v>46169</v>
       </c>
       <c r="C44" s="7">
-        <v>2541.9</v>
+        <v>2541.5</v>
       </c>
       <c r="D44" s="2">
         <f t="shared" si="0"/>
@@ -3288,10 +3337,10 @@
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B45" s="6">
-        <v>46173</v>
+        <v>46170</v>
       </c>
       <c r="C45" s="7">
-        <v>2541.9</v>
+        <v>2541.6</v>
       </c>
       <c r="D45" s="2">
         <f t="shared" si="0"/>
@@ -3304,7 +3353,7 @@
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B46" s="6">
-        <v>46174</v>
+        <v>46171</v>
       </c>
       <c r="C46" s="7">
         <v>2541.8000000000002</v>
@@ -3320,10 +3369,10 @@
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B47" s="6">
-        <v>46175</v>
+        <v>46172</v>
       </c>
       <c r="C47" s="7">
-        <v>2541.6999999999998</v>
+        <v>2541.9</v>
       </c>
       <c r="D47" s="2">
         <f t="shared" si="0"/>
@@ -3336,10 +3385,10 @@
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B48" s="6">
-        <v>46176</v>
+        <v>46173</v>
       </c>
       <c r="C48" s="7">
-        <v>2541.6</v>
+        <v>2541.9</v>
       </c>
       <c r="D48" s="2">
         <f t="shared" si="0"/>
@@ -3352,10 +3401,10 @@
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B49" s="6">
-        <v>46177</v>
+        <v>46174</v>
       </c>
       <c r="C49" s="7">
-        <v>2541.5</v>
+        <v>2541.8000000000002</v>
       </c>
       <c r="D49" s="2">
         <f t="shared" si="0"/>
@@ -3368,10 +3417,10 @@
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B50" s="6">
-        <v>46178</v>
+        <v>46175</v>
       </c>
       <c r="C50" s="7">
-        <v>2541.6</v>
+        <v>2541.6999999999998</v>
       </c>
       <c r="D50" s="2">
         <f t="shared" si="0"/>
@@ -3384,10 +3433,10 @@
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B51" s="6">
-        <v>46179</v>
+        <v>46176</v>
       </c>
       <c r="C51" s="7">
-        <v>2541.6999999999998</v>
+        <v>2541.6</v>
       </c>
       <c r="D51" s="2">
         <f t="shared" si="0"/>
@@ -3400,10 +3449,10 @@
     </row>
     <row r="52" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B52" s="6">
-        <v>46180</v>
+        <v>46177</v>
       </c>
       <c r="C52" s="7">
-        <v>2541.8000000000002</v>
+        <v>2541.5</v>
       </c>
       <c r="D52" s="2">
         <f t="shared" si="0"/>
@@ -3416,74 +3465,74 @@
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B53" s="6">
-        <v>46181</v>
+        <v>46178</v>
       </c>
       <c r="C53" s="7">
-        <v>2542.1999999999998</v>
+        <v>2541.6</v>
       </c>
       <c r="D53" s="2">
-        <f t="shared" ref="D53:D81" si="2">$C$15</f>
+        <f t="shared" si="0"/>
         <v>2545.71</v>
       </c>
       <c r="E53" s="2">
-        <f t="shared" ref="E53:E81" si="3">$C$16</f>
+        <f t="shared" si="1"/>
         <v>2546.77</v>
       </c>
     </row>
     <row r="54" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B54" s="6">
-        <v>46182</v>
+        <v>46179</v>
       </c>
       <c r="C54" s="7">
-        <v>2542.4</v>
+        <v>2541.6999999999998</v>
       </c>
       <c r="D54" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2545.71</v>
       </c>
       <c r="E54" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2546.77</v>
       </c>
     </row>
     <row r="55" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B55" s="6">
-        <v>46183</v>
+        <v>46180</v>
       </c>
       <c r="C55" s="7">
-        <v>2542.4</v>
+        <v>2541.8000000000002</v>
       </c>
       <c r="D55" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>2545.71</v>
       </c>
       <c r="E55" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>2546.77</v>
       </c>
     </row>
     <row r="56" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B56" s="6">
-        <v>46184</v>
+        <v>46181</v>
       </c>
       <c r="C56" s="7">
         <v>2542.1999999999998</v>
       </c>
       <c r="D56" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D56:D84" si="2">$C$18</f>
         <v>2545.71</v>
       </c>
       <c r="E56" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="E56:E84" si="3">$C$19</f>
         <v>2546.77</v>
       </c>
     </row>
     <row r="57" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B57" s="6">
-        <v>46185</v>
+        <v>46182</v>
       </c>
       <c r="C57" s="7">
-        <v>2542</v>
+        <v>2542.4</v>
       </c>
       <c r="D57" s="2">
         <f t="shared" si="2"/>
@@ -3496,10 +3545,10 @@
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B58" s="6">
-        <v>46186</v>
+        <v>46183</v>
       </c>
       <c r="C58" s="7">
-        <v>2541.8000000000002</v>
+        <v>2542.4</v>
       </c>
       <c r="D58" s="2">
         <f t="shared" si="2"/>
@@ -3512,10 +3561,10 @@
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B59" s="6">
-        <v>46187</v>
+        <v>46184</v>
       </c>
       <c r="C59" s="7">
-        <v>2541.6999999999998</v>
+        <v>2542.1999999999998</v>
       </c>
       <c r="D59" s="2">
         <f t="shared" si="2"/>
@@ -3528,10 +3577,10 @@
     </row>
     <row r="60" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B60" s="6">
-        <v>46188</v>
+        <v>46185</v>
       </c>
       <c r="C60" s="7">
-        <v>2541.6</v>
+        <v>2542</v>
       </c>
       <c r="D60" s="2">
         <f t="shared" si="2"/>
@@ -3544,10 +3593,10 @@
     </row>
     <row r="61" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B61" s="6">
-        <v>46189</v>
+        <v>46186</v>
       </c>
       <c r="C61" s="7">
-        <v>2541.5</v>
+        <v>2541.8000000000002</v>
       </c>
       <c r="D61" s="2">
         <f t="shared" si="2"/>
@@ -3560,10 +3609,10 @@
     </row>
     <row r="62" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B62" s="6">
-        <v>46190</v>
+        <v>46187</v>
       </c>
       <c r="C62" s="7">
-        <v>2541.4</v>
+        <v>2541.6999999999998</v>
       </c>
       <c r="D62" s="2">
         <f t="shared" si="2"/>
@@ -3576,10 +3625,10 @@
     </row>
     <row r="63" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B63" s="6">
-        <v>46191</v>
+        <v>46188</v>
       </c>
       <c r="C63" s="7">
-        <v>2541.4</v>
+        <v>2541.6</v>
       </c>
       <c r="D63" s="2">
         <f t="shared" si="2"/>
@@ -3592,10 +3641,10 @@
     </row>
     <row r="64" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B64" s="6">
-        <v>46192</v>
+        <v>46189</v>
       </c>
       <c r="C64" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.5</v>
       </c>
       <c r="D64" s="2">
         <f t="shared" si="2"/>
@@ -3608,10 +3657,10 @@
     </row>
     <row r="65" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B65" s="6">
-        <v>46193</v>
+        <v>46190</v>
       </c>
       <c r="C65" s="7">
-        <v>2541.3000000000002</v>
+        <v>2541.4</v>
       </c>
       <c r="D65" s="2">
         <f t="shared" si="2"/>
@@ -3624,10 +3673,10 @@
     </row>
     <row r="66" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B66" s="6">
-        <v>46194</v>
+        <v>46191</v>
       </c>
       <c r="C66" s="7">
-        <v>2541.1999999999998</v>
+        <v>2541.4</v>
       </c>
       <c r="D66" s="2">
         <f t="shared" si="2"/>
@@ -3640,10 +3689,10 @@
     </row>
     <row r="67" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B67" s="6">
-        <v>46195</v>
+        <v>46192</v>
       </c>
       <c r="C67" s="7">
-        <v>2541.1999999999998</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D67" s="2">
         <f t="shared" si="2"/>
@@ -3656,10 +3705,10 @@
     </row>
     <row r="68" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B68" s="6">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="C68" s="7">
-        <v>2541.1</v>
+        <v>2541.3000000000002</v>
       </c>
       <c r="D68" s="2">
         <f t="shared" si="2"/>
@@ -3672,10 +3721,10 @@
     </row>
     <row r="69" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B69" s="6">
-        <v>46197</v>
+        <v>46194</v>
       </c>
       <c r="C69" s="7">
-        <v>2541.1</v>
+        <v>2541.1999999999998</v>
       </c>
       <c r="D69" s="2">
         <f t="shared" si="2"/>
@@ -3688,10 +3737,10 @@
     </row>
     <row r="70" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B70" s="6">
-        <v>46198</v>
+        <v>46195</v>
       </c>
       <c r="C70" s="7">
-        <v>2541.1</v>
+        <v>2541.1999999999998</v>
       </c>
       <c r="D70" s="2">
         <f t="shared" si="2"/>
@@ -3704,10 +3753,10 @@
     </row>
     <row r="71" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B71" s="6">
-        <v>46199</v>
+        <v>46196</v>
       </c>
       <c r="C71" s="7">
-        <v>2541</v>
+        <v>2541.1</v>
       </c>
       <c r="D71" s="2">
         <f t="shared" si="2"/>
@@ -3720,10 +3769,10 @@
     </row>
     <row r="72" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B72" s="6">
-        <v>46200</v>
+        <v>46197</v>
       </c>
       <c r="C72" s="7">
-        <v>2541</v>
+        <v>2541.1</v>
       </c>
       <c r="D72" s="2">
         <f t="shared" si="2"/>
@@ -3736,10 +3785,10 @@
     </row>
     <row r="73" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B73" s="6">
-        <v>46201</v>
+        <v>46198</v>
       </c>
       <c r="C73" s="7">
-        <v>2541</v>
+        <v>2541.1</v>
       </c>
       <c r="D73" s="2">
         <f t="shared" si="2"/>
@@ -3752,7 +3801,7 @@
     </row>
     <row r="74" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B74" s="6">
-        <v>46202</v>
+        <v>46199</v>
       </c>
       <c r="C74" s="7">
         <v>2541</v>
@@ -3768,7 +3817,7 @@
     </row>
     <row r="75" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B75" s="6">
-        <v>46203</v>
+        <v>46200</v>
       </c>
       <c r="C75" s="7">
         <v>2541</v>
@@ -3784,10 +3833,10 @@
     </row>
     <row r="76" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B76" s="6">
-        <v>46204</v>
+        <v>46201</v>
       </c>
       <c r="C76" s="7">
-        <v>2541.1999999999998</v>
+        <v>2541</v>
       </c>
       <c r="D76" s="2">
         <f t="shared" si="2"/>
@@ -3800,10 +3849,10 @@
     </row>
     <row r="77" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B77" s="6">
-        <v>46205</v>
+        <v>46202</v>
       </c>
       <c r="C77" s="7">
-        <v>2541.5</v>
+        <v>2541</v>
       </c>
       <c r="D77" s="2">
         <f t="shared" si="2"/>
@@ -3816,10 +3865,10 @@
     </row>
     <row r="78" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B78" s="6">
-        <v>46206</v>
+        <v>46203</v>
       </c>
       <c r="C78" s="7">
-        <v>2541.6</v>
+        <v>2541</v>
       </c>
       <c r="D78" s="2">
         <f t="shared" si="2"/>
@@ -3832,10 +3881,10 @@
     </row>
     <row r="79" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B79" s="6">
-        <v>46207</v>
+        <v>46204</v>
       </c>
       <c r="C79" s="7">
-        <v>2541.6</v>
+        <v>2541.1999999999998</v>
       </c>
       <c r="D79" s="2">
         <f t="shared" si="2"/>
@@ -3848,10 +3897,10 @@
     </row>
     <row r="80" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B80" s="6">
-        <v>46208</v>
+        <v>46205</v>
       </c>
       <c r="C80" s="7">
-        <v>2541.6999999999998</v>
+        <v>2541.5</v>
       </c>
       <c r="D80" s="2">
         <f t="shared" si="2"/>
@@ -3864,16 +3913,64 @@
     </row>
     <row r="81" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B81" s="6">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="C81" s="7">
-        <v>2541.9</v>
+        <v>2541.6</v>
       </c>
       <c r="D81" s="2">
         <f t="shared" si="2"/>
         <v>2545.71</v>
       </c>
       <c r="E81" s="2">
+        <f t="shared" si="3"/>
+        <v>2546.77</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B82" s="6">
+        <v>46207</v>
+      </c>
+      <c r="C82" s="7">
+        <v>2541.6</v>
+      </c>
+      <c r="D82" s="2">
+        <f t="shared" si="2"/>
+        <v>2545.71</v>
+      </c>
+      <c r="E82" s="2">
+        <f t="shared" si="3"/>
+        <v>2546.77</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B83" s="6">
+        <v>46208</v>
+      </c>
+      <c r="C83" s="7">
+        <v>2541.6999999999998</v>
+      </c>
+      <c r="D83" s="2">
+        <f t="shared" si="2"/>
+        <v>2545.71</v>
+      </c>
+      <c r="E83" s="2">
+        <f t="shared" si="3"/>
+        <v>2546.77</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B84" s="6">
+        <v>46209</v>
+      </c>
+      <c r="C84" s="7">
+        <v>2541.9</v>
+      </c>
+      <c r="D84" s="2">
+        <f t="shared" si="2"/>
+        <v>2545.71</v>
+      </c>
+      <c r="E84" s="2">
         <f t="shared" si="3"/>
         <v>2546.77</v>
       </c>
@@ -3907,4 +4004,1508 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF887096-C00A-4FD0-835E-FAB42C8173A6}">
+  <dimension ref="B2:F246"/>
+  <sheetFormatPr defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="2.64453125" style="17" customWidth="1"/>
+    <col min="2" max="3" width="17.76171875" style="17" customWidth="1"/>
+    <col min="4" max="4" width="16.234375" style="17" customWidth="1"/>
+    <col min="5" max="16384" width="8.9375" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B2" s="17" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B3" s="17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B4" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E4" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B5" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="17">
+        <v>0</v>
+      </c>
+      <c r="E5" s="17">
+        <v>0</v>
+      </c>
+      <c r="F5" s="17">
+        <v>2545.7391339999999</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B6" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0</v>
+      </c>
+      <c r="E6" s="17">
+        <v>12.399134</v>
+      </c>
+      <c r="F6" s="17">
+        <v>2545.7391339999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B7" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0</v>
+      </c>
+      <c r="E7" s="17">
+        <v>24.197402</v>
+      </c>
+      <c r="F7" s="17">
+        <v>2539.84</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="17">
+        <v>0</v>
+      </c>
+      <c r="E8" s="17">
+        <v>50.197401999999997</v>
+      </c>
+      <c r="F8" s="17">
+        <v>2539.84</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B9" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="17">
+        <v>0</v>
+      </c>
+      <c r="E9" s="17">
+        <v>61.995669999999997</v>
+      </c>
+      <c r="F9" s="17">
+        <v>2545.7391339999999</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B10" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="17">
+        <v>0</v>
+      </c>
+      <c r="E10" s="17">
+        <v>74.394805000000005</v>
+      </c>
+      <c r="F10" s="17">
+        <v>2545.7391339999999</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B11" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0</v>
+      </c>
+      <c r="F11" s="17">
+        <v>2545.8091340000001</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B12" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D12" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E12" s="17">
+        <v>12.399134</v>
+      </c>
+      <c r="F12" s="17">
+        <v>2545.8091340000001</v>
+      </c>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B13" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E13" s="17">
+        <v>24.197402</v>
+      </c>
+      <c r="F13" s="17">
+        <v>2539.91</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B14" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="17">
+        <v>50.197401999999997</v>
+      </c>
+      <c r="F14" s="17">
+        <v>2539.91</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B15" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E15" s="17">
+        <v>61.995669999999997</v>
+      </c>
+      <c r="F15" s="17">
+        <v>2545.8091340000001</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.5">
+      <c r="B16" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" s="17">
+        <v>1000</v>
+      </c>
+      <c r="E16" s="17">
+        <v>74.394805000000005</v>
+      </c>
+      <c r="F16" s="17">
+        <v>2545.8091340000001</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B18" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B19" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B20" s="18">
+        <v>4880508</v>
+      </c>
+      <c r="C20" s="18">
+        <v>2088675</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B21" s="17">
+        <v>4879508</v>
+      </c>
+      <c r="C21" s="17">
+        <v>2088675</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B23" s="17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B24" s="17" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B25" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B26" s="17">
+        <v>0</v>
+      </c>
+      <c r="C26" s="17">
+        <v>0</v>
+      </c>
+      <c r="D26" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B27" s="17">
+        <v>1</v>
+      </c>
+      <c r="C27" s="17">
+        <v>0.25</v>
+      </c>
+      <c r="D27" s="17">
+        <v>23.333333</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B28" s="17">
+        <v>2</v>
+      </c>
+      <c r="C28" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="D28" s="17">
+        <v>46.666666999999997</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B29" s="17">
+        <v>3</v>
+      </c>
+      <c r="C29" s="17">
+        <v>0.75</v>
+      </c>
+      <c r="D29" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B30" s="17">
+        <v>4</v>
+      </c>
+      <c r="C30" s="17">
+        <v>1</v>
+      </c>
+      <c r="D30" s="17">
+        <v>93.333332999999996</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B31" s="17">
+        <v>5</v>
+      </c>
+      <c r="C31" s="17">
+        <v>1.25</v>
+      </c>
+      <c r="D31" s="17">
+        <v>116.666667</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B32" s="17">
+        <v>6</v>
+      </c>
+      <c r="C32" s="17">
+        <v>1.5</v>
+      </c>
+      <c r="D32" s="17">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B33" s="17">
+        <v>7</v>
+      </c>
+      <c r="C33" s="17">
+        <v>1.75</v>
+      </c>
+      <c r="D33" s="17">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B34" s="17">
+        <v>8</v>
+      </c>
+      <c r="C34" s="17">
+        <v>2</v>
+      </c>
+      <c r="D34" s="17">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B35" s="17">
+        <v>9</v>
+      </c>
+      <c r="C35" s="17">
+        <v>2.25</v>
+      </c>
+      <c r="D35" s="17">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B36" s="17">
+        <v>10</v>
+      </c>
+      <c r="C36" s="17">
+        <v>2.5</v>
+      </c>
+      <c r="D36" s="17">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B37" s="17">
+        <v>11</v>
+      </c>
+      <c r="C37" s="17">
+        <v>2.75</v>
+      </c>
+      <c r="D37" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B38" s="17">
+        <v>12</v>
+      </c>
+      <c r="C38" s="17">
+        <v>3</v>
+      </c>
+      <c r="D38" s="17">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B39" s="17">
+        <v>13</v>
+      </c>
+      <c r="C39" s="17">
+        <v>3.25</v>
+      </c>
+      <c r="D39" s="17">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B40" s="17">
+        <v>14</v>
+      </c>
+      <c r="C40" s="17">
+        <v>3.5</v>
+      </c>
+      <c r="D40" s="17">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B41" s="17">
+        <v>15</v>
+      </c>
+      <c r="C41" s="17">
+        <v>3.75</v>
+      </c>
+      <c r="D41" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B42" s="17">
+        <v>16</v>
+      </c>
+      <c r="C42" s="17">
+        <v>4</v>
+      </c>
+      <c r="D42" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="D43" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="D44" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="D45" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="D46" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="D47" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="D48" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D49" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D50" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D51" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D52" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D53" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D54" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D55" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D56" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D57" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D58" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D59" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D60" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D61" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D62" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D63" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D64" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D65" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D66" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D67" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D68" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D69" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D70" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D71" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D72" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D73" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D74" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D75" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D76" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D77" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D78" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D79" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D80" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D81" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D82" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D83" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D84" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D85" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D86" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D87" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D88" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D89" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D90" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D91" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D92" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D93" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D94" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D95" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D96" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D97" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D98" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D99" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D100" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D101" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D102" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D103" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D104" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D105" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D106" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D107" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D108" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D109" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D110" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D111" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D112" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D113" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D114" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D115" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D116" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D117" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D118" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D119" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D120" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D121" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D122" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D123" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D124" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D125" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D126" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D127" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D128" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D129" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D130" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D131" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D132" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D133" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D134" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D135" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D136" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D137" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D138" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D139" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D140" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D141" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D142" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D143" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D144" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D145" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D146" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D147" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D148" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D149" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D150" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D151" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D152" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D153" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D154" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D155" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D156" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D157" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D158" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D159" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D160" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D161" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D162" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D163" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D164" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D165" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D166" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D167" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D168" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D169" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D170" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D171" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D172" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D173" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D174" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D175" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D176" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D177" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D178" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D179" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D180" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D181" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D182" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D183" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D184" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D185" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D186" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D187" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D188" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D189" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D190" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D191" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D192" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D193" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D194" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D195" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D196" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D197" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D198" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D199" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D200" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D201" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D202" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D203" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D204" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D205" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D206" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D207" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D208" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D209" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D210" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D211" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D212" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D213" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D214" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D215" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D216" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D217" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D218" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D219" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D220" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D221" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D222" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D223" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D224" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D225" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D226" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D227" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D228" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D229" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D230" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D231" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D232" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D233" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D234" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D235" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D236" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D237" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D238" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D239" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D240" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D241" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D242" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D243" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D244" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D245" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246" spans="4:4" x14ac:dyDescent="0.5">
+      <c r="D246" s="17">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>